--- a/data/trans_bre/IP11-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP11-Edad-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 1,94</t>
+          <t>-7,15; 1,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 5,65</t>
+          <t>-4,08; 5,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 0,58</t>
+          <t>-4,51; 0,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 1,86</t>
+          <t>-5,07; 2,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-82,72; 85,19</t>
+          <t>-84,36; 64,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,59; 129,93</t>
+          <t>-46,63; 138,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 2,15</t>
+          <t>-4,48; 2,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 2,14</t>
+          <t>-6,89; 1,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 1,55</t>
+          <t>-4,11; 1,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 2,32</t>
+          <t>-3,79; 2,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,88; 51,11</t>
+          <t>-55,54; 45,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,55; 26,98</t>
+          <t>-52,98; 20,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,3; 62,66</t>
+          <t>-70,51; 59,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,02; 207,63</t>
+          <t>-82,93; 148,8</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 4,09</t>
+          <t>-6,19; 4,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 3,81</t>
+          <t>-6,56; 3,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 0,29</t>
+          <t>-6,79; 0,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 1,94</t>
+          <t>-4,24; 2,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-58,42; 84,72</t>
+          <t>-60,43; 88,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-57,74; 76,82</t>
+          <t>-59,09; 74,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-80,41; 11,69</t>
+          <t>-78,5; 13,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-79,07; 113,69</t>
+          <t>-75,26; 152,52</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 2,48</t>
+          <t>-4,47; 2,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,1; -1,71</t>
+          <t>-11,53; -1,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 1,93</t>
+          <t>-7,28; 1,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 2,27</t>
+          <t>-2,9; 2,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,56; 59,74</t>
+          <t>-57,56; 57,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,71; -14,71</t>
+          <t>-71,71; -13,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,37; 42,14</t>
+          <t>-66,98; 32,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,89; 134,23</t>
+          <t>-65,34; 131,61</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,81</t>
+          <t>-3,28; 0,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; -0,17</t>
+          <t>-4,86; -0,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -0,26</t>
+          <t>-3,93; -0,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,03</t>
+          <t>-2,37; 0,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-42,98; 16,24</t>
+          <t>-43,8; 14,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-44,13; -1,12</t>
+          <t>-44,18; -1,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-60,09; -5,16</t>
+          <t>-59,28; -6,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-51,01; 46,13</t>
+          <t>-56,89; 36,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP11-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP11-Edad-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 1,6</t>
+          <t>-7,27; 1,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 5,54</t>
+          <t>-3,7; 5,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 0,63</t>
+          <t>-4,55; 0,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 2,02</t>
+          <t>-5,54; 1,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-84,36; 64,94</t>
+          <t>-86,73; 60,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,63; 138,43</t>
+          <t>-43,72; 156,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 2,13</t>
+          <t>-4,16; 2,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 1,6</t>
+          <t>-7,04; 1,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 1,5</t>
+          <t>-4,22; 1,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 2,0</t>
+          <t>-3,53; 2,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,54; 45,49</t>
+          <t>-53,26; 48,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,98; 20,42</t>
+          <t>-54,65; 24,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,51; 59,7</t>
+          <t>-70,83; 45,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-82,93; 148,8</t>
+          <t>-81,22; 154,84</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,84</t>
+          <t>-0,82</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-23,0%</t>
+          <t>-22,64%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 4,5</t>
+          <t>-6,4; 4,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 3,78</t>
+          <t>-6,15; 4,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 0,37</t>
+          <t>-6,78; 0,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 2,58</t>
+          <t>-4,25; 2,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-60,43; 88,23</t>
+          <t>-59,89; 85,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-59,09; 74,65</t>
+          <t>-54,97; 96,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-78,5; 13,25</t>
+          <t>-77,98; 17,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-75,26; 152,52</t>
+          <t>-81,69; 170,98</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 2,57</t>
+          <t>-4,89; 2,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,53; -1,65</t>
+          <t>-10,65; -0,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 1,7</t>
+          <t>-7,17; 1,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 2,24</t>
+          <t>-2,96; 2,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,56; 57,05</t>
+          <t>-60,4; 66,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,71; -13,0</t>
+          <t>-69,22; -6,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,98; 32,27</t>
+          <t>-65,42; 34,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,34; 131,61</t>
+          <t>-66,33; 134,47</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-18,44%</t>
+          <t>-18,34%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 0,79</t>
+          <t>-3,21; 0,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,86; -0,17</t>
+          <t>-5,08; -0,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; -0,35</t>
+          <t>-3,85; -0,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,88</t>
+          <t>-2,2; 0,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,8; 14,68</t>
+          <t>-43,46; 16,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-44,18; -1,99</t>
+          <t>-44,58; -2,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-59,28; -6,11</t>
+          <t>-60,74; -7,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-56,89; 36,86</t>
+          <t>-55,57; 44,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP11-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP11-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>-1,26</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-38,96%</t>
+          <t>-53,55%</t>
         </is>
       </c>
     </row>
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 1,53</t>
+          <t>-6,81; 1,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 5,61</t>
+          <t>-3,82; 5,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 0,7</t>
+          <t>-4,28; 0,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 1,85</t>
+          <t>-6,25; 1,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-86,73; 60,12</t>
+          <t>-82,72; 85,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-43,72; 156,76</t>
+          <t>-46,59; 129,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,71</t>
+          <t>-0,49</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-23,34%</t>
+          <t>-16,48%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 2,03</t>
+          <t>-4,49; 2,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 1,98</t>
+          <t>-6,73; 2,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 1,31</t>
+          <t>-4,24; 1,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 2,22</t>
+          <t>-3,36; 2,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,26; 48,12</t>
+          <t>-54,88; 51,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,65; 24,95</t>
+          <t>-53,55; 26,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,83; 45,19</t>
+          <t>-71,3; 62,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-81,22; 154,84</t>
+          <t>-77,68; 201,8</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,82</t>
+          <t>-0,96</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-22,64%</t>
+          <t>-25,41%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 4,17</t>
+          <t>-6,04; 4,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 4,43</t>
+          <t>-5,91; 3,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 0,6</t>
+          <t>-7,27; 0,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 2,57</t>
+          <t>-4,33; 2,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-59,89; 85,87</t>
+          <t>-58,42; 84,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,97; 96,57</t>
+          <t>-57,74; 76,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-77,98; 17,38</t>
+          <t>-80,41; 11,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-81,69; 170,98</t>
+          <t>-80,36; 130,51</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-8,37%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 2,52</t>
+          <t>-4,42; 2,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,65; -0,83</t>
+          <t>-11,1; -1,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 1,75</t>
+          <t>-7,37; 1,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 2,22</t>
+          <t>-2,52; 2,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,4; 66,47</t>
+          <t>-58,56; 59,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,22; -6,26</t>
+          <t>-70,71; -14,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,42; 34,09</t>
+          <t>-66,37; 42,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,33; 134,47</t>
+          <t>-60,4; 167,8</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-18,34%</t>
+          <t>-14,0%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,85</t>
+          <t>-3,12; 0,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,08; -0,34</t>
+          <t>-4,91; -0,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; -0,35</t>
+          <t>-3,94; -0,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,98</t>
+          <t>-2,09; 1,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,46; 16,85</t>
+          <t>-42,98; 16,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-44,58; -2,96</t>
+          <t>-44,13; -1,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-60,74; -7,4</t>
+          <t>-60,09; -5,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-55,57; 44,5</t>
+          <t>-50,96; 51,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP11-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP11-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,191 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,47</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,93</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,26</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-42,67%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,56%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-61,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-53,55%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-2.473418713448694</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9304644673431256</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.356206051558509</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.261752855797212</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.4266592943361135</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.1456419133134499</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.6147228498760778</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.5354730365809863</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-6,81; 1,94</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-3,82; 5,65</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,28; 0,58</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-6,25; 1,14</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-82,72; 85,19</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-46,59; 129,93</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-6.806630227301332</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.815181100842684</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.279888905030073</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-6.251592994331974</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.8272410326917976</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.465859071742575</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.941701674028331</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>5.648318161604457</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.5777791895085795</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1.135819974292746</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.8518946148681731</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.299290881925049</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,05</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-2,68</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,39</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-16,61%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-25,53%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-31,52%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-16,48%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-4,49; 2,15</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-6,73; 2,14</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,24; 1,55</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-3,36; 2,58</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-54,88; 51,11</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-53,55; 26,98</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-71,3; 62,66</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-77,68; 201,8</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.051253984112788</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-2.679765581212148</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.393702307311562</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.4918297282072673</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1661054430510996</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.255273472061991</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.3152474474983611</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.16477862510742</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,92</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,02</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,15</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,96</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-11,79%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-12,99%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-48,69%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-25,41%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-4.491617986028735</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-6.73235684450287</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.240383927516929</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.363993493316802</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5487597431251466</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5355075212249515</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.7129614359913962</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.7768310281529548</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-6,04; 4,09</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,91; 3,81</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-7,27; 0,29</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-4,33; 2,24</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-58,42; 84,72</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-57,74; 76,82</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-80,41; 11,69</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-80,36; 130,51</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.147389654791099</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.144681621997952</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.546314068743142</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.578210477020106</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.5111326031927093</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.2698074381039674</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.6265717908695393</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>2.017964755606809</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +811,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,05</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-6,18</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-2,71</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-17,45%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-47,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-32,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.9211156815298869</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.02435128459329</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-3.147981137045138</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.9600280716692315</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.1178545275495259</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1298865760387591</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.486942248390634</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.2541339259239709</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,42; 2,48</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-11,1; -1,71</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-7,37; 1,93</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-2,52; 2,73</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-58,56; 59,74</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-70,71; -14,71</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-66,37; 42,14</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-60,4; 167,8</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-6.03689534872909</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.914914663670283</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-7.268406620563474</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-4.334988037374502</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5841912805884147</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.5774281906407472</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.8040643552266107</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.8035637709833252</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.091558856815922</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.80684269273073</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.2903463466545735</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.238230297275144</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.8471677040077112</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.7682338547830695</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.1168924495011881</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.305084461000954</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.047578405450467</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-6.182825658895965</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-2.706515018387341</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.125580351919001</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1745160081004614</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.4740321564788718</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.3255359367007673</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.04159069639260444</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.418209458510379</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-11.10029124416274</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-7.373781168378539</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-2.516156430960082</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.585586633603567</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.7071042839929012</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.6636603608340874</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.604025194970465</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.477365882600113</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-1.713641045081084</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.92555169741765</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.726161086505221</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.5973789380227608</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.14708352647443</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.4214167301691997</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.677956969052798</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,25</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-2,5</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,15</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-19,48%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-25,55%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-39,23%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-14,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-3,12; 0,81</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-4,91; -0,17</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-3,94; -0,26</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,09; 1,16</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-42,98; 16,24</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-44,13; -1,12</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-60,09; -5,16</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-50,96; 51,94</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-1.253783091072896</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-2.49634625645488</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-2.148717405378005</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.4452213905791414</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1947556359050085</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.2555197408623467</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.392291843862993</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.1400291949360195</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-3.122278990810411</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-4.913528235516504</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.941335189188385</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.087490471059916</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.4298390509560215</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.4412831495001411</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.6008887846541371</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.5096413151972139</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.8142615853996757</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-0.1719679193075936</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-0.2615262235720526</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.156839904508688</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.1623988061282724</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>-0.01116460726314879</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>-0.05163889896638876</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.5193755189529268</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1109,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
